--- a/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clarisse marche avec papa. Ils vont au square. Clarisse tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Clarisse s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clarisse sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Clarisse marche avec papa. Ils vont au square. Clarisse tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Clarisse s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clarisse sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clarisse marche avec papa. Ils vont au square. Clarisse tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Clarisse s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clarisse sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+papa|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Clarisse arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Clarisse s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clarisse donne la main à papa. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Clarisse arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Clarisse s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Clarisse donne la main à papa. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clarisse s'arrête au trottoir</t>
+          <t>Le grain de sable de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un grain de sable brille dans la chaussure. Chouchou et maman vont au square. Le doudou vient aussi. Au bord, Chouchou s'arrête. Pieds au bord, sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clarisse marche avec papa. Ils vont au square. Clarisse tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Clarisse s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clarisse sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Un grain de sable brille dans la chaussure. Il est tout petit, un peu doré. Le doudou gris attend sur le banc de l'entrée. Il sent encore le lit. Une cordelette pend de sa couture. Dehors, une balançoire grince, loin. Le paillasson est rêche et beige. Chouchou vit ici, avec maman. Maman, y a du sable ! Oui. C'est le square d'hier. Tu mets tes chaussures ? En ce moment, Chouchou s'assoit. Maman verse le grain tout doux. Il tombe sur le paillasson. Chouchou enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le doudou. Le doudou est chaud et mou. Maman ouvre la porte. L'air sent le sable et l'herbe. J'entends la balançoire ! Oui. On marche sur le trottoir. Chouchou donne la main à maman. Le doudou pend de l'autre main. La cordelette chatouille les doigts. La balançoire grince encore, plus près. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Chouchou s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le doudou reste contre le ventre. Chouchou serre la main de maman. Bravo, Chouchou. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clarisse marche avec papa. Ils vont au square. Clarisse tient la main de papa. Ils arrivent au bord. Le trottoir est là. Papa s'arrête. Clarisse s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clarisse sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-papa|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un grain de sable brille dans la chaussure.
+narrateur|Il est tout petit, un peu doré.
+narrateur|Le doudou gris attend sur le banc de l'entrée.
+narrateur|Il sent encore le lit.
+narrateur|Une cordelette pend de sa couture.
+narrateur|Dehors, une balançoire grince, loin.
+narrateur|Le paillasson est rêche et beige.
+narrateur|Chouchou vit ici, avec maman.
+enfant-m|Maman, y a du sable !
+maman|Oui.
+maman|C'est le square d'hier.
+maman|Tu mets tes chaussures ?
+narrateur|En ce moment, Chouchou s'assoit.
+narrateur|Maman verse le grain tout doux.
+narrateur|Il tombe sur le paillasson.
+narrateur|Chouchou enfile la chaussure gauche.
+narrateur|Puis la chaussure droite.
+maman|Tu as fini tes chaussures ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|On prend le doudou.
+narrateur|Le doudou est chaud et mou.
+narrateur|Maman ouvre la porte.
+narrateur|L'air sent le sable et l'herbe.
+enfant-m|J'entends la balançoire !
+maman|Oui.
+maman|On marche sur le trottoir.
+narrateur|Chouchou donne la main à maman.
+narrateur|Le doudou pend de l'autre main.
+narrateur|La cordelette chatouille les doigts.
+narrateur|La balançoire grince encore, plus près.
+maman|On reste sur le trottoir.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris et net.
+maman|On va s'arrêter.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+narrateur|Chouchou s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-m|Je m'arrête.
+maman|Oui.
+maman|On attend avec maman.
+maman|Tes pieds sont calmes ?
+enfant-m|Oui.
+narrateur|Le doudou reste contre le ventre.
+narrateur|Chouchou serre la main de maman.
+maman|Bravo, Chouchou.
+maman|Tu as fait du bon travail.
+narrateur|Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clarisse arrive au bord. Que fait-elle ?</t>
+          <t>Chouchou arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1566,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Clarisse arrive au bord. Que fait-elle ?</t>
+          <t>narrateur|Chouchou arrive au bord.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Clarisse s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>Chouchou s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Chouchou. On attend avec maman. La main de maman est chaude. Le doudou sent encore le lit. La balançoire grince tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1743,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Clarisse s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>narrateur|Chouchou s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+maman|Tu t'arrêtes au trottoir ?
+enfant-m|Oui.
+enfant-m|Je m'arrête.
+maman|Bravo, Chouchou.
+maman|On attend avec maman.
+narrateur|La main de maman est chaude.
+narrateur|Le doudou sent encore le lit.
+narrateur|La balançoire grince tout doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clarisse donne la main à papa. Ils attendent un moment.</t>
+          <t>On y va ensemble ? Oui, maman. Ils marchent avec l'adulte. Le square sent le sable chaud. Le seau rouge attend dans le bac. Tu poses le doudou ? Chouchou le pose sur le banc. Il attend. Oui. Tu as fini de le poser ? Oui. Bravo. Le grain doré brille encore au soleil. La balançoire grince, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,10 +1925,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clarisse donne la main à papa. Ils attendent un moment.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|On y va ensemble ?
+enfant-m|Oui, maman.
+narrateur|Ils marchent avec l'adulte.
+narrateur|Le square sent le sable chaud.
+narrateur|Le seau rouge attend dans le bac.
+maman|Tu poses le doudou ?
+narrateur|Chouchou le pose sur le banc.
+enfant-m|Il attend.
+maman|Oui.
+maman|Tu as fini de le poser ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Le grain doré brille encore au soleil.
+narrateur|La balançoire grince, tout près.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Chouchou. Le doudou reste au soleil, sur le banc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2110,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je me suis arrêté.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+maman|Bravo, Chouchou.
+narrateur|Le doudou reste au soleil, sur le banc.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2175,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un grain de sable brille dans la chaussure. Il est tout petit, un peu doré. Le doudou gris attend sur le banc de l'entrée. Il sent encore le lit. Une cordelette pend de sa couture. Dehors, une balançoire grince, loin. Le paillasson est rêche et beige. Chouchou vit ici, avec maman. Maman, y a du sable ! Oui. C'est le square d'hier. Tu mets tes chaussures ? En ce moment, Chouchou s'assoit. Maman verse le grain tout doux. Il tombe sur le paillasson. Chouchou enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le doudou. Le doudou est chaud et mou. Maman ouvre la porte. L'air sent le sable et l'herbe. J'entends la balançoire ! Oui. On marche sur le trottoir. Chouchou donne la main à maman. Le doudou pend de l'autre main. La cordelette chatouille les doigts. La balançoire grince encore, plus près. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Chouchou s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le doudou reste contre le ventre. Chouchou serre la main de maman. Bravo, Chouchou. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Un grain de sable brille dans la chaussure. Il est tout petit, un peu doré. Le doudou gris attend sur le banc de l'entrée. Il sent encore le lit. Une cordelette pend de sa couture. Dehors, une balançoire grince, loin. Le paillasson est rêche et beige. Chouchou vit ici, avec maman. Maman, y a du sable ! Oui. C'est le square d'hier. Tu mets tes chaussures ? En ce moment, Chouchou s'assoit. Maman verse le grain tout doux. Il tombe sur le paillasson. Chouchou enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le doudou. Le doudou est chaud et mou. Maman ouvre la porte. L'air sent le sable et l'herbe. J'entends la balançoire ! Oui. On marche sur le trottoir. Chouchou donne la main à maman. Le doudou pend de l'autre main. La cordelette chatouille les doigts. La balançoire grince encore, plus près. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Chouchou s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le doudou reste contre le ventre. Chouchou serre la main de maman. Bravo, Chouchou. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clarisse marche avec papa. Ils vont au square. Clarisse tient la main de papa. Ils arrivent au bord. Le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Papa s'arrête. Clarisse s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Clarisse sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Clarisse pose les pieds au bord. Les pieds sont calmes. Papa sourit. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un grain de sable brille dans la chaussure. Il est tout petit, un peu doré. Le doudou gris attend sur le banc de l'entrée. Il sent encore le lit. Une cordelette pend de sa couture. Dehors, une balançoire grince, loin. Le paillasson est rêche et beige. Chouchou vit ici, avec maman. Maman, y a du sable ! Oui. C'est le square d'hier. Tu mets tes chaussures ? En ce moment, Chouchou s'assoit. Maman verse le grain tout doux. Il tombe sur le paillasson. Chouchou enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le doudou. Le doudou est chaud et mou. Maman ouvre la porte. L'air sent le sable et l'herbe. J'entends la balançoire ! Oui. On marche sur le trottoir. Chouchou donne la main à maman. Le doudou pend de l'autre main. La cordelette chatouille les doigts. La balançoire grince encore, plus près. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Chouchou s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le doudou reste contre le ventre. Chouchou serre la main de maman. Bravo, Chouchou. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 narrateur|Le doudou reste contre le ventre.
 narrateur|Chouchou serre la main de maman.
 maman|Bravo, Chouchou.
-maman|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1411,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Clarisse arrive au bord. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1569,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Clarisse s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Chouchou. On attend avec maman. La main de maman est chaude. Le doudou sent encore le lit. La balançoire grince tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,7 +1754,6 @@
 narrateur|La balançoire grince tout doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Clarisse donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, maman. Ils marchent avec l'adulte. Le square sent le sable chaud. Le seau rouge attend dans le bac. Tu poses le doudou ? Chouchou le pose sur le banc. Il attend. Oui. Tu as fini de le poser ? Oui. Bravo. Le grain doré brille encore au soleil. La balançoire grince, tout près.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1970,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Chouchou. Le doudou reste au soleil, sur le banc. L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Chouchou. Le doudou reste au soleil, sur le banc.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Chouchou. Le doudou reste au soleil, sur le banc.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,11 +2111,9 @@
 maman|Pieds au bord.
 maman|Sur le trottoir.
 maman|Bravo, Chouchou.
-narrateur|Le doudou reste au soleil, sur le banc.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le doudou reste au soleil, sur le banc.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2137,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2177,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le square</t>
+          <t>entrée, chaussure sablée, trottoir vers le square</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clarisse, papa</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
